--- a/W2_sdm_impacts.xlsx
+++ b/W2_sdm_impacts.xlsx
@@ -474,40 +474,40 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>0.002040521377731024</v>
+        <v>-0.01176155611960746</v>
       </c>
       <c r="C2">
-        <v>-0.09920927386953622</v>
+        <v>-0.07795510232855447</v>
       </c>
       <c r="D2">
-        <v>-0.09716875249180519</v>
+        <v>-0.08971665844816193</v>
       </c>
       <c r="E2">
-        <v>0.05301162854687497</v>
+        <v>0.04496765112255264</v>
       </c>
       <c r="F2">
-        <v>0.03849195796591525</v>
+        <v>-0.2615559369012423</v>
       </c>
       <c r="G2">
-        <v>0.9692954433473659</v>
+        <v>0.7936638188414253</v>
       </c>
       <c r="H2">
-        <v>0.3846729649618429</v>
+        <v>0.304997371005705</v>
       </c>
       <c r="I2">
-        <v>-0.2579055013116847</v>
+        <v>-0.2555927025583978</v>
       </c>
       <c r="J2">
-        <v>0.7964798390269638</v>
+        <v>0.7982653537986748</v>
       </c>
       <c r="K2">
-        <v>0.4238164237628476</v>
+        <v>0.3381938614175333</v>
       </c>
       <c r="L2">
-        <v>-0.2292708518209227</v>
+        <v>-0.2652817471970551</v>
       </c>
       <c r="M2">
-        <v>0.8186584069991505</v>
+        <v>0.7907924245628108</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -515,40 +515,40 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>-1.785205368054307</v>
+        <v>-1.466155351492684</v>
       </c>
       <c r="C3">
-        <v>-3.396604177252589</v>
+        <v>-0.6559758363913888</v>
       </c>
       <c r="D3">
-        <v>-5.181809545306896</v>
+        <v>-2.122131187884073</v>
       </c>
       <c r="E3">
-        <v>0.5909496749787754</v>
+        <v>0.4716565577550725</v>
       </c>
       <c r="F3">
-        <v>-3.020909298441402</v>
+        <v>-3.108523198471137</v>
       </c>
       <c r="G3">
-        <v>0.002520168401944689</v>
+        <v>0.001880248841373389</v>
       </c>
       <c r="H3">
-        <v>3.566239241261449</v>
+        <v>2.502504509534655</v>
       </c>
       <c r="I3">
-        <v>-0.9524330667314241</v>
+        <v>-0.2621277339929224</v>
       </c>
       <c r="J3">
-        <v>0.340877396241362</v>
+        <v>0.7932229655026972</v>
       </c>
       <c r="K3">
-        <v>4.012375592805045</v>
+        <v>2.841887845352951</v>
       </c>
       <c r="L3">
-        <v>-1.291456750609008</v>
+        <v>-0.7467329125440955</v>
       </c>
       <c r="M3">
-        <v>0.1965453428651689</v>
+        <v>0.4552247985954425</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -556,40 +556,40 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>0.1854354846670733</v>
+        <v>0.1306604471835709</v>
       </c>
       <c r="C4">
-        <v>0.4759003758381601</v>
+        <v>0.3343226658020212</v>
       </c>
       <c r="D4">
-        <v>0.6613358605052334</v>
+        <v>0.4649831129855921</v>
       </c>
       <c r="E4">
-        <v>0.07044656761762977</v>
+        <v>0.03547276500052954</v>
       </c>
       <c r="F4">
-        <v>2.632285588044274</v>
+        <v>3.683401820569114</v>
       </c>
       <c r="G4">
-        <v>0.008481253720871607</v>
+        <v>0.0002301419480565947</v>
       </c>
       <c r="H4">
-        <v>0.4656131335524534</v>
+        <v>0.2285693732107879</v>
       </c>
       <c r="I4">
-        <v>1.022093969315726</v>
+        <v>1.462674815552419</v>
       </c>
       <c r="J4">
-        <v>0.3067364272021098</v>
+        <v>0.1435563805680418</v>
       </c>
       <c r="K4">
-        <v>0.5310201679510026</v>
+        <v>0.2609870209547882</v>
       </c>
       <c r="L4">
-        <v>1.24540629606794</v>
+        <v>1.78163309150206</v>
       </c>
       <c r="M4">
-        <v>0.2129824401374449</v>
+        <v>0.07480908440419376</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -597,40 +597,40 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>4.743832743061177</v>
+        <v>3.108857830039126</v>
       </c>
       <c r="C5">
-        <v>17.71155342507264</v>
+        <v>11.818084800745</v>
       </c>
       <c r="D5">
-        <v>22.45538616813382</v>
+        <v>14.92694263078412</v>
       </c>
       <c r="E5">
-        <v>3.819393298998346</v>
+        <v>2.771619560477006</v>
       </c>
       <c r="F5">
-        <v>1.242038295533814</v>
+        <v>1.121675526602244</v>
       </c>
       <c r="G5">
-        <v>0.2142224329536901</v>
+        <v>0.2620004259013475</v>
       </c>
       <c r="H5">
-        <v>26.51031499779364</v>
+        <v>17.98512337326085</v>
       </c>
       <c r="I5">
-        <v>0.6681004517127281</v>
+        <v>0.6571033489998396</v>
       </c>
       <c r="J5">
-        <v>0.5040694735226625</v>
+        <v>0.5111144656640929</v>
       </c>
       <c r="K5">
-        <v>30.10406741896912</v>
+        <v>20.53772357477796</v>
       </c>
       <c r="L5">
-        <v>0.7459253215060324</v>
+        <v>0.726806093013914</v>
       </c>
       <c r="M5">
-        <v>0.455712528046837</v>
+        <v>0.4673447500208145</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -638,40 +638,40 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>132.0049261805014</v>
+        <v>130.7187619741368</v>
       </c>
       <c r="C6">
-        <v>982.5780565525326</v>
+        <v>866.9223018599581</v>
       </c>
       <c r="D6">
-        <v>1114.582982733034</v>
+        <v>997.6410638340949</v>
       </c>
       <c r="E6">
-        <v>55.79299141528655</v>
+        <v>42.77267607803785</v>
       </c>
       <c r="F6">
-        <v>2.365976851786688</v>
+        <v>3.056127742291436</v>
       </c>
       <c r="G6">
-        <v>0.01798256873115234</v>
+        <v>0.002242157077523954</v>
       </c>
       <c r="H6">
-        <v>457.999164690577</v>
+        <v>338.4376148666819</v>
       </c>
       <c r="I6">
-        <v>2.145370848473839</v>
+        <v>2.561542404798764</v>
       </c>
       <c r="J6">
-        <v>0.0319232079626901</v>
+        <v>0.01042085189305952</v>
       </c>
       <c r="K6">
-        <v>510.8519434446149</v>
+        <v>378.6718498231838</v>
       </c>
       <c r="L6">
-        <v>2.181812161107838</v>
+        <v>2.634579423582533</v>
       </c>
       <c r="M6">
-        <v>0.02912339867923364</v>
+        <v>0.008424159256247954</v>
       </c>
     </row>
   </sheetData>
